--- a/exports/trend_1d/NESTLEIND_full_report.xlsx
+++ b/exports/trend_1d/NESTLEIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>5.73</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42039</v>
+        <v>42040</v>
       </c>
       <c r="H2" t="n">
-        <v>348.9</v>
+        <v>345</v>
       </c>
       <c r="I2" t="n">
         <v>345.044893</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5</v>
+        <v>1.35</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>8.07</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42068</v>
+        <v>42072</v>
       </c>
       <c r="H3" t="n">
-        <v>364.8</v>
+        <v>369.2</v>
       </c>
       <c r="I3" t="n">
         <v>367.7449438819373</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.74</v>
+        <v>-7.01</v>
       </c>
       <c r="L3" t="n">
-        <v>6.75</v>
+        <v>7.59</v>
       </c>
       <c r="M3" t="n">
         <v>2.73</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>7.57</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42088</v>
+        <v>42089</v>
       </c>
       <c r="H4" t="n">
-        <v>352.1</v>
+        <v>342.2</v>
       </c>
       <c r="I4" t="n">
         <v>348.9037568678345</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.63</v>
+        <v>-7.31</v>
       </c>
       <c r="L4" t="n">
-        <v>5.58</v>
+        <v>8.4</v>
       </c>
       <c r="M4" t="n">
         <v>0.71</v>
       </c>
       <c r="N4" t="n">
-        <v>1.79</v>
+        <v>2.81</v>
       </c>
       <c r="O4" t="n">
         <v>1.21</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>7.81</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42139</v>
+        <v>42142</v>
       </c>
       <c r="H5" t="n">
-        <v>351.6</v>
+        <v>353.9</v>
       </c>
       <c r="I5" t="n">
         <v>352.5852669617359</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.75</v>
+        <v>-3.42</v>
       </c>
       <c r="L5" t="n">
-        <v>4.85</v>
+        <v>7.36</v>
       </c>
       <c r="M5" t="n">
         <v>1.5</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>6.51</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42157</v>
+        <v>42158</v>
       </c>
       <c r="H6" t="n">
-        <v>340.2</v>
+        <v>309.4</v>
       </c>
       <c r="I6" t="n">
         <v>330.8669353351698</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.87</v>
+        <v>-12.57</v>
       </c>
       <c r="L6" t="n">
-        <v>7.71</v>
+        <v>15.51</v>
       </c>
       <c r="M6" t="n">
-        <v>1.24</v>
+        <v>4.47</v>
       </c>
       <c r="N6" t="n">
-        <v>4.34</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0.65</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>16.36</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42220</v>
+        <v>42221</v>
       </c>
       <c r="H7" t="n">
-        <v>317.5</v>
+        <v>341.9</v>
       </c>
       <c r="I7" t="n">
         <v>321.1472292502207</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.62</v>
+        <v>-10.5</v>
       </c>
       <c r="L7" t="n">
-        <v>5.56</v>
+        <v>13.09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.89</v>
+        <v>7.09</v>
       </c>
       <c r="N7" t="n">
-        <v>7.11</v>
+        <v>7.69</v>
       </c>
       <c r="O7" t="n">
         <v>-9.050000000000001</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.29</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42234</v>
+        <v>42235</v>
       </c>
       <c r="H8" t="n">
-        <v>308.2</v>
+        <v>304.9</v>
       </c>
       <c r="I8" t="n">
         <v>306.7074350912509</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.859999999999999</v>
+        <v>-10.82</v>
       </c>
       <c r="L8" t="n">
         <v>12.14</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>10.29</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42277</v>
+        <v>42278</v>
       </c>
       <c r="H9" t="n">
-        <v>318.4</v>
+        <v>321.1</v>
       </c>
       <c r="I9" t="n">
         <v>319.6705854028162</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.43</v>
+        <v>-5.31</v>
       </c>
       <c r="L9" t="n">
-        <v>4.92</v>
+        <v>5.51</v>
       </c>
       <c r="M9" t="n">
         <v>1.69</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>7.45</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42317</v>
+        <v>42318</v>
       </c>
       <c r="H10" t="n">
-        <v>305.6</v>
+        <v>303.6</v>
       </c>
       <c r="I10" t="n">
         <v>303.7148912773603</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.83</v>
+        <v>-5.45</v>
       </c>
       <c r="L10" t="n">
-        <v>5.01</v>
+        <v>5.79</v>
       </c>
       <c r="M10" t="n">
         <v>0.95</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42458</v>
+        <v>42459</v>
       </c>
       <c r="H11" t="n">
-        <v>266.8</v>
+        <v>274</v>
       </c>
       <c r="I11" t="n">
         <v>268.4178100786389</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K11" t="n">
-        <v>12.12</v>
+        <v>9.75</v>
       </c>
       <c r="L11" t="n">
         <v>4.15</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.74</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42492</v>
+        <v>42493</v>
       </c>
       <c r="H12" t="n">
-        <v>287.7</v>
+        <v>279.6</v>
       </c>
       <c r="I12" t="n">
         <v>282.1535950402871</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>2.04</v>
       </c>
       <c r="L12" t="n">
         <v>2.26</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>10.41</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42502</v>
+        <v>42503</v>
       </c>
       <c r="H13" t="n">
-        <v>285.5</v>
+        <v>306.1</v>
       </c>
       <c r="I13" t="n">
         <v>298.0633086396539</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.11</v>
+        <v>-9.48</v>
       </c>
       <c r="L13" t="n">
-        <v>3.61</v>
+        <v>10.16</v>
       </c>
       <c r="M13" t="n">
         <v>0.39</v>
       </c>
       <c r="N13" t="n">
-        <v>1.93</v>
+        <v>7.22</v>
       </c>
       <c r="O13" t="n">
         <v>-2.82</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.64</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42594</v>
+        <v>42598</v>
       </c>
       <c r="H14" t="n">
-        <v>344.8</v>
+        <v>337.4</v>
       </c>
       <c r="I14" t="n">
         <v>337.5689675218406</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K14" t="n">
-        <v>12.64</v>
+        <v>10.23</v>
       </c>
       <c r="L14" t="n">
         <v>7.02</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.88</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42647</v>
+        <v>42648</v>
       </c>
       <c r="H15" t="n">
-        <v>334</v>
+        <v>338.8</v>
       </c>
       <c r="I15" t="n">
         <v>335.9078491461935</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K15" t="n">
-        <v>1.01</v>
+        <v>-0.41</v>
       </c>
       <c r="L15" t="n">
         <v>2.1</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.87</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42681</v>
+        <v>42682</v>
       </c>
       <c r="H16" t="n">
-        <v>322.9</v>
+        <v>322.6</v>
       </c>
       <c r="I16" t="n">
         <v>322.8970868667103</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.69</v>
+        <v>-4.78</v>
       </c>
       <c r="L16" t="n">
         <v>6.2</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.25</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42769</v>
+        <v>42772</v>
       </c>
       <c r="H17" t="n">
-        <v>304.4</v>
+        <v>315.3</v>
       </c>
       <c r="I17" t="n">
         <v>307.9790851750505</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K17" t="n">
-        <v>5.64</v>
+        <v>2.26</v>
       </c>
       <c r="L17" t="n">
         <v>1.43</v>
@@ -1410,7 +1613,7 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="O17" t="n">
         <v>-0.09</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.33</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42870</v>
+        <v>42871</v>
       </c>
       <c r="H18" t="n">
-        <v>330.5</v>
+        <v>324</v>
       </c>
       <c r="I18" t="n">
         <v>326.9459944819143</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K18" t="n">
-        <v>4.82</v>
+        <v>2.76</v>
       </c>
       <c r="L18" t="n">
         <v>5.46</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.39</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42921</v>
+        <v>42922</v>
       </c>
       <c r="H19" t="n">
-        <v>345.4</v>
+        <v>345.9</v>
       </c>
       <c r="I19" t="n">
         <v>345.8100622708429</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.6</v>
+        <v>-6.76</v>
       </c>
       <c r="L19" t="n">
         <v>7.84</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>4.81</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42957</v>
+        <v>42958</v>
       </c>
       <c r="H20" t="n">
-        <v>332.1</v>
+        <v>327.2</v>
       </c>
       <c r="I20" t="n">
         <v>329.2577725009234</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.99</v>
+        <v>-5.41</v>
       </c>
       <c r="L20" t="n">
-        <v>5.23</v>
+        <v>5.58</v>
       </c>
       <c r="M20" t="n">
-        <v>0.71</v>
+        <v>1.2</v>
       </c>
       <c r="N20" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="O20" t="n">
         <v>0.14</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>5.07</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42971</v>
+        <v>42975</v>
       </c>
       <c r="H21" t="n">
-        <v>330.1</v>
+        <v>352.4</v>
       </c>
       <c r="I21" t="n">
         <v>343.7863241237256</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.89</v>
+        <v>-7.7</v>
       </c>
       <c r="L21" t="n">
-        <v>3.18</v>
+        <v>8.1</v>
       </c>
       <c r="M21" t="n">
         <v>1.51</v>
       </c>
       <c r="N21" t="n">
-        <v>1.65</v>
+        <v>6.76</v>
       </c>
       <c r="O21" t="n">
         <v>-1.48</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.83</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43124</v>
+        <v>43125</v>
       </c>
       <c r="H22" t="n">
-        <v>379.6</v>
+        <v>374.6</v>
       </c>
       <c r="I22" t="n">
         <v>378.3940037045202</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K22" t="n">
-        <v>7.72</v>
+        <v>6.3</v>
       </c>
       <c r="L22" t="n">
         <v>5.65</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>6</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>5.49</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43145</v>
+        <v>43146</v>
       </c>
       <c r="H23" t="n">
-        <v>363.2</v>
+        <v>379.2</v>
       </c>
       <c r="I23" t="n">
         <v>372.038782178763</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23" t="n">
-        <v>3.04</v>
+        <v>-1.23</v>
       </c>
       <c r="L23" t="n">
-        <v>1.79</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>1.17</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>2.47</v>
+        <v>4.41</v>
       </c>
       <c r="O23" t="n">
         <v>-1.32</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.19</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H24" t="n">
-        <v>542</v>
+        <v>519.3</v>
       </c>
       <c r="I24" t="n">
         <v>535.7073805597428</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K24" t="n">
-        <v>42.93</v>
+        <v>36.95</v>
       </c>
       <c r="L24" t="n">
         <v>2.06</v>
@@ -1809,7 +2096,7 @@
         <v>0.6</v>
       </c>
       <c r="N24" t="n">
-        <v>4.05</v>
+        <v>4.19</v>
       </c>
       <c r="O24" t="n">
         <v>4.41</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>138</v>
+        <v>139</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>8</v>
+      </c>
+      <c r="U24" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.05</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43406</v>
+        <v>43409</v>
       </c>
       <c r="H25" t="n">
-        <v>511.5</v>
+        <v>516.6</v>
       </c>
       <c r="I25" t="n">
         <v>514.5346256174573</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K25" t="n">
-        <v>1.5</v>
+        <v>0.52</v>
       </c>
       <c r="L25" t="n">
         <v>4.37</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43504</v>
+        <v>43507</v>
       </c>
       <c r="H26" t="n">
-        <v>562.1</v>
+        <v>542.2</v>
       </c>
       <c r="I26" t="n">
         <v>552.5710643644069</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K26" t="n">
-        <v>8.81</v>
+        <v>4.96</v>
       </c>
       <c r="L26" t="n">
         <v>2.44</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.24</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43551</v>
+        <v>43552</v>
       </c>
       <c r="H27" t="n">
-        <v>544.6</v>
+        <v>553.6</v>
       </c>
       <c r="I27" t="n">
         <v>545.5049714370327</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.44</v>
+        <v>-2.1</v>
       </c>
       <c r="L27" t="n">
         <v>4.21</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,25 +2351,25 @@
         <v>9.07</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43588</v>
+        <v>43591</v>
       </c>
       <c r="H28" t="n">
-        <v>524.3</v>
+        <v>518.2</v>
       </c>
       <c r="I28" t="n">
         <v>519.455167201607</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.29</v>
+        <v>-6.39</v>
       </c>
       <c r="L28" t="n">
-        <v>6.25</v>
+        <v>6.94</v>
       </c>
       <c r="M28" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="N28" t="n">
         <v>2.9</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>7.59</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H29" t="n">
-        <v>533</v>
+        <v>551.8</v>
       </c>
       <c r="I29" t="n">
         <v>548.4540143826976</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.86</v>
+        <v>-6.48</v>
       </c>
       <c r="L29" t="n">
-        <v>6.02</v>
+        <v>6.95</v>
       </c>
       <c r="M29" t="n">
         <v>2.04</v>
       </c>
       <c r="N29" t="n">
-        <v>2.89</v>
+        <v>3.53</v>
       </c>
       <c r="O29" t="n">
         <v>-1.16</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.94</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H30" t="n">
-        <v>802.4</v>
+        <v>778.3</v>
       </c>
       <c r="I30" t="n">
         <v>780.7550474962017</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K30" t="n">
-        <v>45.42</v>
+        <v>41.05</v>
       </c>
       <c r="L30" t="n">
         <v>3.04</v>
@@ -2151,7 +2510,7 @@
         <v>1.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
         <v>3.53</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>197</v>
+        <v>198</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>11</v>
+      </c>
+      <c r="U30" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43917</v>
+        <v>43920</v>
       </c>
       <c r="H31" t="n">
-        <v>755.4</v>
+        <v>782.9</v>
       </c>
       <c r="I31" t="n">
         <v>766.3045028396386</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K31" t="n">
-        <v>2.94</v>
+        <v>-0.59</v>
       </c>
       <c r="L31" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="M31" t="n">
         <v>7.29</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>22.06</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44062</v>
+        <v>44063</v>
       </c>
       <c r="H32" t="n">
-        <v>817.3</v>
+        <v>810.6</v>
       </c>
       <c r="I32" t="n">
         <v>810.7425622936743</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K32" t="n">
-        <v>4.39</v>
+        <v>3.54</v>
       </c>
       <c r="L32" t="n">
         <v>6.19</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>5.18</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44111</v>
+        <v>44112</v>
       </c>
       <c r="H33" t="n">
-        <v>805.7</v>
+        <v>815.2</v>
       </c>
       <c r="I33" t="n">
         <v>814.6668440200433</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6</v>
+        <v>-0.57</v>
       </c>
       <c r="L33" t="n">
         <v>3.06</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.73</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H34" t="n">
-        <v>879.5</v>
+        <v>870.8</v>
       </c>
       <c r="I34" t="n">
         <v>873.7143468521059</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K34" t="n">
-        <v>7.89</v>
+        <v>6.82</v>
       </c>
       <c r="L34" t="n">
         <v>5.69</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>6.42</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44292</v>
+        <v>44293</v>
       </c>
       <c r="H35" t="n">
-        <v>854.1</v>
+        <v>870.5</v>
       </c>
       <c r="I35" t="n">
         <v>859.9410947863784</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K35" t="n">
-        <v>1.92</v>
+        <v>0.03</v>
       </c>
       <c r="L35" t="n">
-        <v>1.63</v>
+        <v>2.58</v>
       </c>
       <c r="M35" t="n">
         <v>0.9399999999999999</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>7.03</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44315</v>
+        <v>44316</v>
       </c>
       <c r="H36" t="n">
-        <v>825.1</v>
+        <v>815.4</v>
       </c>
       <c r="I36" t="n">
         <v>821.6366360867415</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K36" t="n">
-        <v>-5.22</v>
+        <v>-6.33</v>
       </c>
       <c r="L36" t="n">
-        <v>5.34</v>
+        <v>6.63</v>
       </c>
       <c r="M36" t="n">
         <v>1.23</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>7.18</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44336</v>
+        <v>44337</v>
       </c>
       <c r="H37" t="n">
-        <v>864.3</v>
+        <v>874.8</v>
       </c>
       <c r="I37" t="n">
         <v>873.7447307503223</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>-6</v>
+        <v>-7.28</v>
       </c>
       <c r="L37" t="n">
-        <v>7.31</v>
+        <v>7.62</v>
       </c>
       <c r="M37" t="n">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
       <c r="N37" t="n">
         <v>3.03</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>5.53</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44474</v>
+        <v>44475</v>
       </c>
       <c r="H38" t="n">
-        <v>969.8</v>
+        <v>957.8</v>
       </c>
       <c r="I38" t="n">
         <v>959.4039493770161</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K38" t="n">
-        <v>10.86</v>
+        <v>9.49</v>
       </c>
       <c r="L38" t="n">
         <v>1.23</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.31</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H39" t="n">
-        <v>994.4</v>
+        <v>996.8</v>
       </c>
       <c r="I39" t="n">
         <v>995.4231872635112</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.82</v>
+        <v>-4.07</v>
       </c>
       <c r="L39" t="n">
         <v>5.45</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>4.48</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44579</v>
+        <v>44580</v>
       </c>
       <c r="H40" t="n">
-        <v>969</v>
+        <v>946.8</v>
       </c>
       <c r="I40" t="n">
         <v>952.1456955458644</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.79</v>
+        <v>-5.02</v>
       </c>
       <c r="L40" t="n">
-        <v>4.13</v>
+        <v>6.84</v>
       </c>
       <c r="M40" t="n">
         <v>0.93</v>
       </c>
       <c r="N40" t="n">
-        <v>1.59</v>
+        <v>2.29</v>
       </c>
       <c r="O40" t="n">
         <v>0.24</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.08</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44656</v>
+        <v>44657</v>
       </c>
       <c r="H41" t="n">
-        <v>901.2</v>
+        <v>910.8</v>
       </c>
       <c r="I41" t="n">
         <v>906.6695256006647</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K41" t="n">
-        <v>4.82</v>
+        <v>3.8</v>
       </c>
       <c r="L41" t="n">
         <v>2.68</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.21</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H42" t="n">
-        <v>880.2</v>
+        <v>849.8</v>
       </c>
       <c r="I42" t="n">
         <v>870.7590128549516</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.36</v>
+        <v>-6.7</v>
       </c>
       <c r="L42" t="n">
-        <v>3.9</v>
+        <v>6.81</v>
       </c>
       <c r="M42" t="n">
         <v>1.58</v>
       </c>
       <c r="N42" t="n">
-        <v>3.31</v>
+        <v>3.45</v>
       </c>
       <c r="O42" t="n">
         <v>1.07</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>10.21</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44706</v>
+        <v>44707</v>
       </c>
       <c r="H43" t="n">
-        <v>864.2</v>
+        <v>882.6</v>
       </c>
       <c r="I43" t="n">
         <v>864.8761575389398</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.69</v>
+        <v>-3.86</v>
       </c>
       <c r="L43" t="n">
-        <v>3.55</v>
+        <v>4.32</v>
       </c>
       <c r="M43" t="n">
         <v>1.66</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.19</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44819</v>
+        <v>44820</v>
       </c>
       <c r="H44" t="n">
-        <v>950.4</v>
+        <v>920.2</v>
       </c>
       <c r="I44" t="n">
         <v>937.0671465555611</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K44" t="n">
-        <v>7.68</v>
+        <v>4.26</v>
       </c>
       <c r="L44" t="n">
         <v>6.89</v>
@@ -2949,7 +3476,7 @@
         <v>1.13</v>
       </c>
       <c r="N44" t="n">
-        <v>2.54</v>
+        <v>3.18</v>
       </c>
       <c r="O44" t="n">
         <v>2.13</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>7.48</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44852</v>
+        <v>44853</v>
       </c>
       <c r="H45" t="n">
-        <v>969.4</v>
+        <v>987</v>
       </c>
       <c r="I45" t="n">
         <v>979.8942479314513</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.35</v>
+        <v>-7.26</v>
       </c>
       <c r="L45" t="n">
-        <v>6.09</v>
+        <v>7.85</v>
       </c>
       <c r="M45" t="n">
         <v>1.36</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>6.87</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44945</v>
+        <v>44946</v>
       </c>
       <c r="H46" t="n">
-        <v>984</v>
+        <v>960</v>
       </c>
       <c r="I46" t="n">
         <v>970.8131603724795</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.3</v>
+        <v>-2.74</v>
       </c>
       <c r="L46" t="n">
-        <v>2.46</v>
+        <v>2.99</v>
       </c>
       <c r="M46" t="n">
         <v>0.8</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>5.74</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45007</v>
+        <v>45008</v>
       </c>
       <c r="H47" t="n">
-        <v>941</v>
+        <v>952.2</v>
       </c>
       <c r="I47" t="n">
         <v>947.0255809544635</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K47" t="n">
-        <v>1.98</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L47" t="n">
         <v>3.12</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.87</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45147</v>
+        <v>45148</v>
       </c>
       <c r="H48" t="n">
-        <v>1110.9</v>
+        <v>1099.5</v>
       </c>
       <c r="I48" t="n">
         <v>1106.861096774278</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K48" t="n">
-        <v>16.67</v>
+        <v>15.47</v>
       </c>
       <c r="L48" t="n">
         <v>1.75</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>6</v>
+      </c>
+      <c r="U48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>5.28</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45184</v>
+        <v>45187</v>
       </c>
       <c r="H49" t="n">
-        <v>1131.1</v>
+        <v>1141</v>
       </c>
       <c r="I49" t="n">
         <v>1137.713883307457</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.87</v>
+        <v>-3.77</v>
       </c>
       <c r="L49" t="n">
-        <v>3.23</v>
+        <v>3.87</v>
       </c>
       <c r="M49" t="n">
         <v>1.05</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.14</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45300</v>
+        <v>45301</v>
       </c>
       <c r="H50" t="n">
-        <v>1296.3</v>
+        <v>1289</v>
       </c>
       <c r="I50" t="n">
         <v>1291.32392028992</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K50" t="n">
-        <v>13.61</v>
+        <v>12.97</v>
       </c>
       <c r="L50" t="n">
         <v>2.47</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.69</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="H51" t="n">
-        <v>1292</v>
+        <v>1299.4</v>
       </c>
       <c r="I51" t="n">
         <v>1297.12721708904</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.23</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L51" t="n">
         <v>1.72</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>5.35</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45398</v>
+        <v>45400</v>
       </c>
       <c r="H52" t="n">
-        <v>1273</v>
+        <v>1231.3</v>
       </c>
       <c r="I52" t="n">
         <v>1237.645121038173</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.03</v>
+        <v>-5.24</v>
       </c>
       <c r="L52" t="n">
-        <v>5.03</v>
+        <v>7.24</v>
       </c>
       <c r="M52" t="n">
         <v>1.03</v>
       </c>
       <c r="N52" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="O52" t="n">
         <v>0.57</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.85</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45450</v>
+        <v>45453</v>
       </c>
       <c r="H53" t="n">
-        <v>1251.2</v>
+        <v>1274.1</v>
       </c>
       <c r="I53" t="n">
         <v>1259.206383492091</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.62</v>
+        <v>-3.48</v>
       </c>
       <c r="L53" t="n">
         <v>4.88</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>7.92</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45497</v>
+        <v>45498</v>
       </c>
       <c r="H54" t="n">
-        <v>1270.7</v>
+        <v>1240.3</v>
       </c>
       <c r="I54" t="n">
         <v>1242.164353162154</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.27</v>
+        <v>-2.65</v>
       </c>
       <c r="L54" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="M54" t="n">
         <v>1.24</v>
       </c>
       <c r="N54" t="n">
-        <v>1.63</v>
+        <v>2.39</v>
       </c>
       <c r="O54" t="n">
         <v>1.83</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>7.89</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45552</v>
+        <v>45553</v>
       </c>
       <c r="H55" t="n">
-        <v>1273.4</v>
+        <v>1298.6</v>
       </c>
       <c r="I55" t="n">
         <v>1295.368860460799</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.67</v>
+        <v>-4.7</v>
       </c>
       <c r="L55" t="n">
-        <v>4.22</v>
+        <v>4.86</v>
       </c>
       <c r="M55" t="n">
         <v>0.7</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.6</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H56" t="n">
-        <v>1337.4</v>
+        <v>1299.1</v>
       </c>
       <c r="I56" t="n">
         <v>1299.864052665025</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K56" t="n">
-        <v>2.99</v>
+        <v>0.04</v>
       </c>
       <c r="L56" t="n">
         <v>1.97</v>
@@ -3633,7 +4304,7 @@
         <v>0.93</v>
       </c>
       <c r="N56" t="n">
-        <v>2.03</v>
+        <v>2.86</v>
       </c>
       <c r="O56" t="n">
         <v>1.98</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.77</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45687</v>
+        <v>45688</v>
       </c>
       <c r="H57" t="n">
-        <v>1108.7</v>
+        <v>1156.6</v>
       </c>
       <c r="I57" t="n">
         <v>1130.673261205077</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K57" t="n">
-        <v>14.66</v>
+        <v>10.97</v>
       </c>
       <c r="L57" t="n">
         <v>3.09</v>
@@ -3690,7 +4373,7 @@
         <v>1.32</v>
       </c>
       <c r="N57" t="n">
-        <v>2.21</v>
+        <v>4.32</v>
       </c>
       <c r="O57" t="n">
         <v>-2.86</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45719</v>
+        <v>45720</v>
       </c>
       <c r="H58" t="n">
-        <v>1092.8</v>
+        <v>1073.2</v>
       </c>
       <c r="I58" t="n">
         <v>1076.020245072378</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.52</v>
+        <v>-7.21</v>
       </c>
       <c r="L58" t="n">
-        <v>7.02</v>
+        <v>8.44</v>
       </c>
       <c r="M58" t="n">
-        <v>0.75</v>
+        <v>1.17</v>
       </c>
       <c r="N58" t="n">
         <v>3.89</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>6.73</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="H59" t="n">
-        <v>1137.7</v>
+        <v>1172.4</v>
       </c>
       <c r="I59" t="n">
         <v>1145.410558832868</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.01</v>
+        <v>-9.24</v>
       </c>
       <c r="L59" t="n">
-        <v>6.63</v>
+        <v>10.07</v>
       </c>
       <c r="M59" t="n">
         <v>0.92</v>
       </c>
       <c r="N59" t="n">
-        <v>2.36</v>
+        <v>3.05</v>
       </c>
       <c r="O59" t="n">
         <v>-1.79</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>9.01</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45861</v>
+        <v>45862</v>
       </c>
       <c r="H60" t="n">
-        <v>1226.2</v>
+        <v>1161</v>
       </c>
       <c r="I60" t="n">
         <v>1171.081563746895</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K60" t="n">
-        <v>4.59</v>
+        <v>-0.97</v>
       </c>
       <c r="L60" t="n">
         <v>3.1</v>
@@ -3861,7 +4580,7 @@
         <v>1.66</v>
       </c>
       <c r="N60" t="n">
-        <v>2.24</v>
+        <v>5.32</v>
       </c>
       <c r="O60" t="n">
         <v>3.05</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.75</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="H61" t="n">
-        <v>1144.1</v>
+        <v>1161.4</v>
       </c>
       <c r="I61" t="n">
         <v>1158.443860479326</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K61" t="n">
-        <v>1.46</v>
+        <v>-0.03</v>
       </c>
       <c r="L61" t="n">
         <v>6.59</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.41</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="H62" t="n">
-        <v>1246.9</v>
+        <v>1214.8</v>
       </c>
       <c r="I62" t="n">
         <v>1226.95249678709</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K62" t="n">
-        <v>7.36</v>
+        <v>4.6</v>
       </c>
       <c r="L62" t="n">
         <v>2.69</v>
@@ -3975,7 +4718,7 @@
         <v>0.99</v>
       </c>
       <c r="N62" t="n">
-        <v>1.72</v>
+        <v>2.57</v>
       </c>
       <c r="O62" t="n">
         <v>1.51</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>5.95</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="H63" t="n">
-        <v>1259.7</v>
+        <v>1272.6</v>
       </c>
       <c r="I63" t="n">
         <v>1266.801477076705</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.7</v>
+        <v>-4.76</v>
       </c>
       <c r="L63" t="n">
-        <v>4.06</v>
+        <v>5.12</v>
       </c>
       <c r="M63" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="N63" t="n">
         <v>1.92</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>5.11</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H64" t="n">
-        <v>1279.7</v>
+        <v>1245.3</v>
       </c>
       <c r="I64" t="n">
         <v>1251.752382467718</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K64" t="n">
-        <v>0.5600000000000001</v>
+        <v>-2.15</v>
       </c>
       <c r="L64" t="n">
-        <v>1.67</v>
+        <v>2.56</v>
       </c>
       <c r="M64" t="n">
         <v>2.31</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>7.36</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H65" t="n">
-        <v>1226.1</v>
+        <v>1256.6</v>
       </c>
       <c r="I65" t="n">
         <v>1255.28165045815</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K65" t="n">
-        <v>1.54</v>
+        <v>-0.91</v>
       </c>
       <c r="L65" t="n">
         <v>1.98</v>
@@ -4146,7 +4925,7 @@
         <v>1.49</v>
       </c>
       <c r="N65" t="n">
-        <v>2.07</v>
+        <v>2.49</v>
       </c>
       <c r="O65" t="n">
         <v>-2.69</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>7.94</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H66" t="n">
-        <v>1391.5</v>
+        <v>1382.9</v>
       </c>
       <c r="I66" t="n">
         <v>1391.311913334146</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K66" t="n">
-        <v>10.74</v>
+        <v>10.05</v>
       </c>
       <c r="L66" t="n">
         <v>1.93</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>7.03</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="H67" t="n">
-        <v>1459.8</v>
+        <v>1473.7</v>
       </c>
       <c r="I67" t="n">
         <v>1470.858986574509</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K67" t="n">
-        <v>-5.56</v>
+        <v>-6.57</v>
       </c>
       <c r="L67" t="n">
-        <v>5.84</v>
+        <v>7.01</v>
       </c>
       <c r="M67" t="n">
         <v>2.49</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,25 +5111,25 @@
         <v>6.87</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="H68" t="n">
-        <v>1438.2</v>
+        <v>1425</v>
       </c>
       <c r="I68" t="n">
         <v>1427.205718710217</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.41</v>
+        <v>-3.3</v>
       </c>
       <c r="L68" t="n">
         <v>4.65</v>
       </c>
       <c r="M68" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="N68" t="n">
         <v>3.9</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>7.21</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H69" t="n">
-        <v>1334</v>
+        <v>1383.2</v>
       </c>
       <c r="I69" t="n">
         <v>1382.68535959482</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K69" t="n">
-        <v>6.39</v>
+        <v>2.93</v>
       </c>
       <c r="L69" t="n">
         <v>0.21</v>
@@ -4374,7 +5201,7 @@
         <v>0.53</v>
       </c>
       <c r="N69" t="n">
-        <v>3.42</v>
+        <v>3.69</v>
       </c>
       <c r="O69" t="n">
         <v>-0.92</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="H70" t="n">
-        <v>1265.5</v>
+        <v>1242.7</v>
       </c>
       <c r="I70" t="n">
         <v>1260.583989820412</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K70" t="n">
-        <v>-8.51</v>
+        <v>-10.16</v>
       </c>
       <c r="L70" t="n">
-        <v>9.609999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="M70" t="n">
         <v>0.23</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>7</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9449,7 +10308,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.7</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="6">
@@ -9459,7 +10318,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -9469,7 +10328,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8">
@@ -9479,7 +10338,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -9489,7 +10348,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -9499,7 +10358,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>121.8</v>
+        <v>122.8</v>
       </c>
     </row>
     <row r="11">
@@ -9509,7 +10368,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -9519,7 +10378,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -9529,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="14">
@@ -9539,7 +10398,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.05</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="15">
@@ -9549,7 +10408,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.27</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="16">
@@ -9559,7 +10418,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.25</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="17">
@@ -9569,7 +10428,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>45.42</v>
+        <v>41.05</v>
       </c>
     </row>
     <row r="18">
@@ -9579,7 +10438,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.8</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="19">
@@ -9589,7 +10448,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.28</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="20">
@@ -9599,7 +10458,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.15</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="21">
@@ -9609,7 +10468,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.14</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="22">
@@ -9619,7 +10478,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -9629,7 +10488,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -9639,7 +10498,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="25">
@@ -9659,7 +10518,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="27">
@@ -9669,7 +10528,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.82</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -9679,7 +10538,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
